--- a/Horarios/Colectivos/322-Lujan/DomingoLujan.xlsx
+++ b/Horarios/Colectivos/322-Lujan/DomingoLujan.xlsx
@@ -158,7 +158,7 @@
     <tableColumn id="1" name="Tipo"/>
     <tableColumn id="2" name="Formacion"/>
     <tableColumn id="3" name="Marcos Paz"/>
-    <tableColumn id="4" name="Las Heras"/>
+    <tableColumn id="4" name="General Las Heras"/>
     <tableColumn id="5" name="Villars"/>
     <tableColumn id="6" name="Plomer"/>
     <tableColumn id="7" name="Luján"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Las Heras</t>
+          <t>General Las Heras</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -512,23 +512,23 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>135_337850-1</t>
+          <t>322 H · 09:24</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.3916666666666667</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.2305555555555556</v>
+        <v>0.4256944444444444</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.25</v>
+        <v>0.4458333333333334</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2659722222222222</v>
+        <v>0.4611111111111111</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.3006944444444444</v>
+        <v>0.5013888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -539,23 +539,23 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>135_337851-1</t>
+          <t>322 H · 14:50</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.375</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3972222222222222</v>
+        <v>0.6520833333333333</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.675</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4326388888888889</v>
+        <v>0.6923611111111111</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.4673611111111111</v>
+        <v>0.7395833333333334</v>
       </c>
     </row>
     <row r="4">
@@ -564,26 +564,12 @@
           <t>322 Luján</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>135_337852-1</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.5638888888888889</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.5993055555555555</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.6340277777777777</v>
-      </c>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -728,7 +714,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -752,7 +738,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46264</v>
+        <v>46276</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
@@ -777,7 +763,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/sube/cuandosubo</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-line-322-Buenos_Aires-1602-855399-579299-13</t>
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
@@ -803,7 +789,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>https://cuandosubo.sube.gob.ar/onebusaway-api-webapp/api/where</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-time-322-Buenos_Aires-1602-855399-579299-6997957-0</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
@@ -829,7 +815,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
